--- a/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/Inputs_IS2026_Unscaled_Guw.xlsx
+++ b/HazardAnalysis/gm-selection/2020_NBC_MyCopy_new-main/GMSelection_NGA_KiK_mixed/Inputs_IS2026_Unscaled_Guw.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\psb\Downloads\GitHub\ida-spo-msa\HazardAnalysis\gm-selection\2020_NBC_MyCopy_new-main\GMSelection_NGA_KiK_mixed\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\StaticDynamicAnalysis\ida-spo-msa\HazardAnalysis\gm-selection\2020_NBC_MyCopy_new-main\GMSelection_NGA_KiK_mixed\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20FEC310-2A7D-4393-A2BD-A8B26895DDAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECD4BF19-4A99-4F7B-ABD9-212F7DFE0C65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1519,7 +1519,7 @@
         <v>20</v>
       </c>
       <c r="K17" s="31" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="L17" s="35" t="s">
         <v>36</v>
